--- a/GameData/tables/10_League.xlsx
+++ b/GameData/tables/10_League.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="league_syn" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'league_unit'!$A$1:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'league_param'!$A$1:$C$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'league_unit'!$A$1:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'league_param'!$A$1:$C$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'league_enemy'!$A$1:$J$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'league_tier'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'league_round'!$A$1:$E$10</definedName>
@@ -534,18 +534,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11.6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="30.8" customWidth="1" min="8" max="8"/>
-    <col width="30.8" customWidth="1" min="9" max="9"/>
+    <col width="33.2" customWidth="1" min="8" max="8"/>
+    <col width="33.2" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,8 +1062,148 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>league.skill.blender.name</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>league.skill.blender.desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>league.skill.purifier.name</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>league.skill.purifier.desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>470</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>league.skill.router.name</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>league.skill.router.desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>league.skill.tv.name</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>league.skill.tv.desc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1074,10 +1214,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11.6" customWidth="1" min="1" max="1"/>
     <col width="10.4" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1596,8 +1736,173 @@
         <v>4</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>dmg</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>exec</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>radius</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>dmg</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>airMul</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>dmg</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>stun</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>stun</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>brk</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>dur</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C34"/>
+  <autoFilter ref="A1:C45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
